--- a/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/50_CROSS_ROLE/valcanary_site_registry.xlsx
+++ b/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/50_CROSS_ROLE/valcanary_site_registry.xlsx
@@ -578,7 +578,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -605,7 +605,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -632,7 +632,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VALSITE-DELTA</t>
+          <t>Site: Validation Delta Site</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -686,7 +686,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VALSITE-ECHO</t>
+          <t>Site: Validation Echo Site</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
